--- a/reports/Debug-snowbowl-20251230/For The Day (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Day (Prior Year)_Payroll_history.xlsx
@@ -19,6 +19,108 @@
     <t>department</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D6781</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6760</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>D8030</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D6721</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
     <t>D1020</t>
   </si>
   <si>
@@ -26,108 +128,6 @@
   </si>
   <si>
     <t>D1070</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6760</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>D6781</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D6721</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D8030</t>
   </si>
   <si>
     <t>total</t>
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>1151.86</v>
+        <v>897.27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -521,7 +521,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>578.40</v>
+        <v>289.75</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -529,7 +529,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>998.04</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -537,7 +537,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>1036.50</v>
+        <v>892.60</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -545,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>2917.66</v>
+        <v>569.69</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>928.53</v>
+        <v>1791.97</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -561,7 +561,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>309.26</v>
+        <v>321.10</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -569,7 +569,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>765.80</v>
+        <v>183.14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -577,7 +577,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>680.26</v>
+        <v>1378.87</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>373.13</v>
+        <v>564.43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -593,7 +593,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>897.27</v>
+        <v>662.90</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -601,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>289.75</v>
+        <v>1015.87</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -609,7 +609,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>208.58</v>
+        <v>208.26</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -617,7 +617,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>892.60</v>
+        <v>8083.35</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>569.69</v>
+        <v>311.82</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -633,7 +633,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>2306.31</v>
+        <v>931.04</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -641,7 +641,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>2850.58</v>
+        <v>897.29</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -649,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>400.69</v>
+        <v>1036.50</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -657,7 +657,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>208.58</v>
+        <v>2917.66</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -665,7 +665,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>773.07</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -673,7 +673,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>1791.97</v>
+        <v>309.26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -681,7 +681,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>321.10</v>
+        <v>765.80</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -689,7 +689,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>183.14</v>
+        <v>680.26</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -697,7 +697,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>1378.87</v>
+        <v>373.13</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -705,7 +705,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>564.43</v>
+        <v>824.18</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -713,7 +713,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>662.90</v>
+        <v>2306.31</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -721,7 +721,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>1015.87</v>
+        <v>2850.58</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -729,7 +729,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>208.26</v>
+        <v>400.69</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -737,7 +737,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>8083.35</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -745,7 +745,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>311.82</v>
+        <v>773.07</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -753,7 +753,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>931.04</v>
+        <v>6123.31</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -761,7 +761,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>897.29</v>
+        <v>2402.35</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -769,7 +769,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>6123.31</v>
+        <v>686.46</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -777,7 +777,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>2402.35</v>
+        <v>637.01</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -785,7 +785,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>686.46</v>
+        <v>1151.86</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -793,7 +793,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>637.01</v>
+        <v>578.40</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -801,7 +801,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>824.18</v>
+        <v>998.04</v>
       </c>
     </row>
   </sheetData>
